--- a/docs/design-docs/09_プログラム設計書_点検計画・実施.xlsx
+++ b/docs/design-docs/09_プログラム設計書_点検計画・実施.xlsx
@@ -14,7 +14,770 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="254">
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>承認者</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>システム開発部</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>新規</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 年間点検計画一覧</t>
+  </si>
+  <si>
+    <t>文書管理情報</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>STRUTSLAB-001</t>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+  </si>
+  <si>
+    <t>点検計画</t>
+  </si>
+  <si>
+    <t>プログラムID</t>
+  </si>
+  <si>
+    <t>PG-INS-PLAN-001</t>
+  </si>
+  <si>
+    <t>プログラム名</t>
+  </si>
+  <si>
+    <t>年間点検計画一覧</t>
+  </si>
+  <si>
+    <t>文書番号</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-INS-PLAN-001</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>プログラム概要</t>
+  </si>
+  <si>
+    <t>年度×設備×月matrix形式で点検計画と実績を表示。動的column(12ヶ月)table生成。計画lock/解除。</t>
+  </si>
+  <si>
+    <t>入出力定義</t>
+  </si>
+  <si>
+    <t>項目名</t>
+  </si>
+  <si>
+    <t>型</t>
+  </si>
+  <si>
+    <t>Formプロパティ</t>
+  </si>
+  <si>
+    <t>必須</t>
+  </si>
+  <si>
+    <t>入力</t>
+  </si>
+  <si>
+    <t>年度</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>planYear</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>設備種別</t>
+  </si>
+  <si>
+    <t>eqpType</t>
+  </si>
+  <si>
+    <t>出力</t>
+  </si>
+  <si>
+    <t>matrix data</t>
+  </si>
+  <si>
+    <t>Map</t>
+  </si>
+  <si>
+    <t>monthlyMatrix</t>
+  </si>
+  <si>
+    <t>行=設備 列=月</t>
+  </si>
+  <si>
+    <t>処理詳細</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>処理内容</t>
+  </si>
+  <si>
+    <t>関連DAO</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>年度→会計期間(4月〜3月)開始月計算</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>対象設備一覧→行生成</t>
+  </si>
+  <si>
+    <t>EqpDao.findByType()</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>各月計画/実績count</t>
+  </si>
+  <si>
+    <t>PlanDao.countMonthly()</t>
+  </si>
+  <si>
+    <t>GROUP BY</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>JSP matrix描画</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>計画lock:plan_locked=1</t>
+  </si>
+  <si>
+    <t>PlanDao.lockYear()</t>
+  </si>
+  <si>
+    <t>入力検証ルール</t>
+  </si>
+  <si>
+    <t>対象項目</t>
+  </si>
+  <si>
+    <t>検証ルール</t>
+  </si>
+  <si>
+    <t>エラーメッセージ(ja)</t>
+  </si>
+  <si>
+    <t>空不可</t>
+  </si>
+  <si>
+    <t>空可</t>
+  </si>
+  <si>
+    <t>状態遷移</t>
+  </si>
+  <si>
+    <t>遷移元</t>
+  </si>
+  <si>
+    <t>遷移先</t>
+  </si>
+  <si>
+    <t>トリガー</t>
+  </si>
+  <si>
+    <t>表示</t>
+  </si>
+  <si>
+    <t>matrix表示</t>
+  </si>
+  <si>
+    <t>計画lock</t>
+  </si>
+  <si>
+    <t>lock</t>
+  </si>
+  <si>
+    <t>計画解除</t>
+  </si>
+  <si>
+    <t>解除</t>
+  </si>
+  <si>
+    <t>struts-config.xml</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>値</t>
+  </si>
+  <si>
+    <t>action path</t>
+  </si>
+  <si>
+    <t>/ins/plan/yearly</t>
+  </si>
+  <si>
+    <t>action class</t>
+  </si>
+  <si>
+    <t>YearlyPlanAction</t>
+  </si>
+  <si>
+    <t>form bean</t>
+  </si>
+  <si>
+    <t>YearlyPlanForm</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 点検計画登録Wizard</t>
+  </si>
+  <si>
+    <t>PG-INS-PLAN-002</t>
+  </si>
+  <si>
+    <t>点検計画登録Wizard</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-INS-PLAN-002</t>
+  </si>
+  <si>
+    <t>4stepWizard方式の点検計画登録。step間data hidden持回り。一時保存→session復元可能。</t>
+  </si>
+  <si>
+    <t>入力(全step)</t>
+  </si>
+  <si>
+    <t>wizardForm</t>
+  </si>
+  <si>
+    <t>PlanWizardForm</t>
+  </si>
+  <si>
+    <t>planWizardForm</t>
+  </si>
+  <si>
+    <t>hidden持回り</t>
+  </si>
+  <si>
+    <t>Step1出力</t>
+  </si>
+  <si>
+    <t>選択設備</t>
+  </si>
+  <si>
+    <t>EqpDto</t>
+  </si>
+  <si>
+    <t>selectedEqp</t>
+  </si>
+  <si>
+    <t>Step2出力</t>
+  </si>
+  <si>
+    <t>template一覧</t>
+  </si>
+  <si>
+    <t>List</t>
+  </si>
+  <si>
+    <t>tmplList</t>
+  </si>
+  <si>
+    <t>Step3出力</t>
+  </si>
+  <si>
+    <t>担当者一覧</t>
+  </si>
+  <si>
+    <t>empList</t>
+  </si>
+  <si>
+    <t>班連動</t>
+  </si>
+  <si>
+    <t>Step4出力</t>
+  </si>
+  <si>
+    <t>確認data</t>
+  </si>
+  <si>
+    <t>PlanConfirmDto</t>
+  </si>
+  <si>
+    <t>confirmData</t>
+  </si>
+  <si>
+    <t>step param分岐(step1/2/3/confirm)</t>
+  </si>
+  <si>
+    <t>Step1:設備選択→validation→step2</t>
+  </si>
+  <si>
+    <t>Step2:template選択→step3</t>
+  </si>
+  <si>
+    <t>Step3:日程・担当者→validation→confirm</t>
+  </si>
+  <si>
+    <t>班→担当者連動</t>
+  </si>
+  <si>
+    <t>Step4:全入力表示→一時保存or確定</t>
+  </si>
+  <si>
+    <t>一時保存=session 確定=DB</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>途中離脱再開:session復元(切時最初)</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>「戻る」:前step(hidden値維持,修正→再進可)</t>
+  </si>
+  <si>
+    <t>Step1:selectedEqp</t>
+  </si>
+  <si>
+    <t>Step2:selectedTmpl</t>
+  </si>
+  <si>
+    <t>Step3:planDate</t>
+  </si>
+  <si>
+    <t>未来日</t>
+  </si>
+  <si>
+    <t>Step1</t>
+  </si>
+  <si>
+    <t>Step2</t>
+  </si>
+  <si>
+    <t>進む</t>
+  </si>
+  <si>
+    <t>戻る</t>
+  </si>
+  <si>
+    <t>Step3</t>
+  </si>
+  <si>
+    <t>確認</t>
+  </si>
+  <si>
+    <t>一覧</t>
+  </si>
+  <si>
+    <t>確定</t>
+  </si>
+  <si>
+    <t>session</t>
+  </si>
+  <si>
+    <t>一時保存</t>
+  </si>
+  <si>
+    <t>/ins/plan/wizard</t>
+  </si>
+  <si>
+    <t>PlanWizardAction</t>
+  </si>
+  <si>
+    <t>scope</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 点検実施入力</t>
+  </si>
+  <si>
+    <t>点検実施</t>
+  </si>
+  <si>
+    <t>PG-INS-EXEC-001</t>
+  </si>
+  <si>
+    <t>点検実施入力</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-INS-EXEC-001</t>
+  </si>
+  <si>
+    <t>nest checklist形式で点検結果入力。判定値(○/×/△)条件付validation。写真添付(max5枚/項目)。総合判定異常→異常報告。</t>
+  </si>
+  <si>
+    <t>判定[{i}]</t>
+  </si>
+  <si>
+    <t>String[]</t>
+  </si>
+  <si>
+    <t>execJudge</t>
+  </si>
+  <si>
+    <t>radio</t>
+  </si>
+  <si>
+    <t>実測値[{i}]</t>
+  </si>
+  <si>
+    <t>execValue</t>
+  </si>
+  <si>
+    <t>×時必須</t>
+  </si>
+  <si>
+    <t>所見[{i}]</t>
+  </si>
+  <si>
+    <t>execNote</t>
+  </si>
+  <si>
+    <t>×/△時必須</t>
+  </si>
+  <si>
+    <t>写真[{i}][{j}]</t>
+  </si>
+  <si>
+    <t>FormFile[][]</t>
+  </si>
+  <si>
+    <t>execPhoto</t>
+  </si>
+  <si>
+    <t>総合判定</t>
+  </si>
+  <si>
+    <t>summaryJudge</t>
+  </si>
+  <si>
+    <t>総合所見</t>
+  </si>
+  <si>
+    <t>summaryNote</t>
+  </si>
+  <si>
+    <t>点検項目master→checklist構築</t>
+  </si>
+  <si>
+    <t>ChkItemDao.findByTmpl()</t>
+  </si>
+  <si>
+    <t>3階層</t>
+  </si>
+  <si>
+    <t>各項目判定応validation</t>
+  </si>
+  <si>
+    <t>Validator+Action内追加</t>
+  </si>
+  <si>
+    <t>×→実測値+所見必須 △→所見必須 ○→任意</t>
+  </si>
+  <si>
+    <t>写真保存:項目{i}/写真{j}→filesystem</t>
+  </si>
+  <si>
+    <t>総合判定異常→異常報告用data→session</t>
+  </si>
+  <si>
+    <t>Forward:inc.create</t>
+  </si>
+  <si>
+    <t>execJudge[{i}]</t>
+  </si>
+  <si>
+    <t>execValue[{i}]</t>
+  </si>
+  <si>
+    <t>×時:空不可 数値</t>
+  </si>
+  <si>
+    <t>execNote[{i}]</t>
+  </si>
+  <si>
+    <t>×/△時:空不可</t>
+  </si>
+  <si>
+    <t>jpg/png max5MB</t>
+  </si>
+  <si>
+    <t>判定入力</t>
+  </si>
+  <si>
+    <t>各項目判定</t>
+  </si>
+  <si>
+    <t>error→再表示</t>
+  </si>
+  <si>
+    <t>保存→NG</t>
+  </si>
+  <si>
+    <t>保存→一覧</t>
+  </si>
+  <si>
+    <t>保存→OK</t>
+  </si>
+  <si>
+    <t>異常報告登録</t>
+  </si>
+  <si>
+    <t>異常→異常報告へ</t>
+  </si>
+  <si>
+    <t>/ins/exec/input</t>
+  </si>
+  <si>
+    <t>ExecInputAction</t>
+  </si>
+  <si>
+    <t>ExecForm(ValidatorForm)</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 点検実施詳細・修正</t>
+  </si>
+  <si>
+    <t>PG-INS-EXEC-002</t>
+  </si>
+  <si>
+    <t>点検実施詳細・修正</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-INS-EXEC-002</t>
+  </si>
+  <si>
+    <t>実施済点検結果照会と修正申請。修正理由必須。承認flow連携。</t>
+  </si>
+  <si>
+    <t>修正理由</t>
+  </si>
+  <si>
+    <t>modifyReason</t>
+  </si>
+  <si>
+    <t>申請時○</t>
+  </si>
+  <si>
+    <t>実施結果全data</t>
+  </si>
+  <si>
+    <t>ExecResultDto</t>
+  </si>
+  <si>
+    <t>execResult</t>
+  </si>
+  <si>
+    <t>指定点検ID→全data取得</t>
+  </si>
+  <si>
+    <t>ExecDao.findById()</t>
+  </si>
+  <si>
+    <t>修正申請:理由必須→approval_status=申請中</t>
+  </si>
+  <si>
+    <t>ExecDao.requestModify()</t>
+  </si>
+  <si>
+    <t>承認済data修正不可(button非表示)</t>
+  </si>
+  <si>
+    <t>申請時:空不可 max500</t>
+  </si>
+  <si>
+    <t>修正申請→申請中</t>
+  </si>
+  <si>
+    <t>修正申請→理由OK</t>
+  </si>
+  <si>
+    <t>申請中→操作不可</t>
+  </si>
+  <si>
+    <t>承認待ち</t>
+  </si>
+  <si>
+    <t>申請中</t>
+  </si>
+  <si>
+    <t>承認→表示(修正反映)</t>
+  </si>
+  <si>
+    <t>承認者操作</t>
+  </si>
+  <si>
+    <t>差戻→表示(取消)</t>
+  </si>
+  <si>
+    <t>差戻</t>
+  </si>
+  <si>
+    <t>/ins/exec/detail</t>
+  </si>
+  <si>
+    <t>ExecDetailAction</t>
+  </si>
+  <si>
+    <t>ExecForm</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 点検実施承認一覧</t>
+  </si>
+  <si>
+    <t>PG-INS-APPR-001</t>
+  </si>
+  <si>
+    <t>点検実施承認一覧</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-INS-APPR-001</t>
+  </si>
+  <si>
+    <t>点検結果修正申請の承認/差戻一覧。一括操作。差戻時理由必須。操作後通知message。</t>
+  </si>
+  <si>
+    <t>期間from/to</t>
+  </si>
+  <si>
+    <t>apprDateFrom/To</t>
+  </si>
+  <si>
+    <t>担当班</t>
+  </si>
+  <si>
+    <t>apprTeam</t>
+  </si>
+  <si>
+    <t>承認待ちlist</t>
+  </si>
+  <si>
+    <t>List&amp;lt;ApprovalDto&amp;gt;</t>
+  </si>
+  <si>
+    <t>approvalList</t>
+  </si>
+  <si>
+    <t>検索条件→承認待ち一覧</t>
+  </si>
+  <si>
+    <t>ExecDao.findPendingApprovals()</t>
+  </si>
+  <si>
+    <t>一括承認:選択行status=承認済</t>
+  </si>
+  <si>
+    <t>ExecDao.bulkApprove()</t>
+  </si>
+  <si>
+    <t>一括差戻:理由→reject_reason→status=差戻</t>
+  </si>
+  <si>
+    <t>ExecDao.bulkReject()</t>
+  </si>
+  <si>
+    <t>操作結果message→request</t>
+  </si>
+  <si>
+    <t>空可 YYYYMMDD</t>
+  </si>
+  <si>
+    <t>rejectReason</t>
+  </si>
+  <si>
+    <t>一括差戻時:空不可</t>
+  </si>
+  <si>
+    <t>一括承認→通知</t>
+  </si>
+  <si>
+    <t>承認→confirmOK</t>
+  </si>
+  <si>
+    <t>一括差戻→理由→通知</t>
+  </si>
+  <si>
+    <t>差戻→confirm→理由必須</t>
+  </si>
+  <si>
+    <t>検索結果表示</t>
+  </si>
+  <si>
+    <t>検索</t>
+  </si>
+  <si>
+    <t>全件表示</t>
+  </si>
+  <si>
+    <t>クリア</t>
+  </si>
+  <si>
+    <t>/ins/approval/list</t>
+  </si>
+  <si>
+    <t>ApprovalListAction</t>
+  </si>
+  <si>
+    <t>ApprovalForm</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
